--- a/ValueSet-mhi-an-subtyp-vs.xlsx
+++ b/ValueSet-mhi-an-subtyp-vs.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:19:25+00:00</t>
+    <t>2026-09-30T09:40:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -122,7 +122,7 @@
     <t>used-codesystem</t>
   </si>
   <si>
-    <t>https://bih-cei.github.io/PCOR-MII/CodeSystem/mhi-an-subtyp|0.1.0</t>
+    <t>https://bih-cei.github.io/PCOR-MII/CodeSystem/mhi-an-subtyp|0.3.0</t>
   </si>
   <si>
     <t>Level</t>

--- a/ValueSet-mhi-an-subtyp-vs.xlsx
+++ b/ValueSet-mhi-an-subtyp-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:40:42+00:00</t>
+    <t>2026-09-30T19:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mhi-an-subtyp-vs.xlsx
+++ b/ValueSet-mhi-an-subtyp-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:42:59+00:00</t>
+    <t>2026-09-30T19:54:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mhi-an-subtyp-vs.xlsx
+++ b/ValueSet-mhi-an-subtyp-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:54:40+00:00</t>
+    <t>2026-10-01T09:59:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mhi-an-subtyp-vs.xlsx
+++ b/ValueSet-mhi-an-subtyp-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T09:59:00+00:00</t>
+    <t>2026-10-01T11:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mhi-an-subtyp-vs.xlsx
+++ b/ValueSet-mhi-an-subtyp-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:16:03+00:00</t>
+    <t>2026-10-01T11:25:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mhi-an-subtyp-vs.xlsx
+++ b/ValueSet-mhi-an-subtyp-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:25:55+00:00</t>
+    <t>2026-10-01T11:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mhi-an-subtyp-vs.xlsx
+++ b/ValueSet-mhi-an-subtyp-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:30:23+00:00</t>
+    <t>2026-10-01T13:09:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mhi-an-subtyp-vs.xlsx
+++ b/ValueSet-mhi-an-subtyp-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:09:50+00:00</t>
+    <t>2026-10-01T14:39:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mhi-an-subtyp-vs.xlsx
+++ b/ValueSet-mhi-an-subtyp-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T14:39:45+00:00</t>
+    <t>2026-10-01T14:59:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mhi-an-subtyp-vs.xlsx
+++ b/ValueSet-mhi-an-subtyp-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T14:59:54+00:00</t>
+    <t>2026-10-13T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mhi-an-subtyp-vs.xlsx
+++ b/ValueSet-mhi-an-subtyp-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T13:38:01+00:00</t>
+    <t>2026-10-13T14:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mhi-an-subtyp-vs.xlsx
+++ b/ValueSet-mhi-an-subtyp-vs.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T14:06:39+00:00</t>
+    <t>2026-10-14T13:27:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
